--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A9B42CD-17C4-4CB2-B11E-36AEF85DD7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA389FE-1868-4DA8-B0D7-1A9B33D1522C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{C6E74B48-9CDE-4D63-A8F7-4935BA93D084}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>질문</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,39 +64,673 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>팀플유형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>리더쉽형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>에디</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>협동형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여행스타일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>즉흥형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뽀로로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계획형</t>
+    <t>주제를 정하는데 의견이 갈린다면?</t>
+  </si>
+  <si>
+    <t>프로젝트가 끝난 후 가장 듣고 싶은 말은?</t>
+  </si>
+  <si>
+    <t>마무리 단계에서 불안해지면?</t>
+  </si>
+  <si>
+    <t>처음 팀원들을 만난 날, 드는 걱정은?</t>
+  </si>
+  <si>
+    <t>새 프로젝트를 시작할 때 방향은?</t>
+  </si>
+  <si>
+    <t>함께 일할 팀을 꾸린다면 더 끌리는 사람은?</t>
+  </si>
+  <si>
+    <t>협업할 때 더 편한 방식은?</t>
+  </si>
+  <si>
+    <t>팀플에서 내가 더 편한 역할은?</t>
+  </si>
+  <si>
+    <t>더 좋은 아이디어는?</t>
+  </si>
+  <si>
+    <t>팀원으로서 중요한 덕목은</t>
+  </si>
+  <si>
+    <t>팀 프로젝트에서 더 중요한 건?</t>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>결과물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이 좋아야지.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>성실한 게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 최고지.”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“뻔한 건 재미없잖아. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>새롭고 참신한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 게 좋아.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“내가 앞에서 방향 잡아볼게.” 주도적으로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이끄는 역할</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>계획</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부터 딱 세워둬야 마음이 편해.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“같이 하면 뭔가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>재밌는 결과물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 나올 듯?”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“일단 잘된 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사례</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부터 보자.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“이 팀에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>빌런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있으면 어떡하지?.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“거의다 왔는데 뭐, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>너무 걱정하진 말자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“너 덕분에 프로젝트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>결과물이 좋아졌어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“일단 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기준부터 정하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 제일 괜찮은 안으로 가자.”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“팀플은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>협력과 분위기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지.”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“일단 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">잘하는 게 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중요하지.”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“아이디어도 결국 설득이야. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>구조가 탄탄한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 게 좋아.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“뭐가 필요해?” 필요한 곳을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>채워주는 역할</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>“하다 보면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 바뀔 수도 있지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“팀에 있으면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>든든할 것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 같아.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“남들 다 하는 방식 말고, 우리만의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>새로운 방법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>을 해보면 어때?”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“내가 혹시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>민폐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가 되면 어떡하지?”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“어떻게든 되게 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만들어야지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“너 덕분에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>팀 분위기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가 좋았어.”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“제일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>재밌어 보이는 거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 하면 안 돼?”</t>
+    </r>
+  </si>
+  <si>
+    <t>[포비, 크롱, 뽀로로]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[루피, 에디, 뽀로로]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[루피, 포비]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[크롱, 에디, 뽀로로]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[루피, 포비, 크롱]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에디, 뽀로로]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[포비, 크롱]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[루피, 포비, 에디]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[뽀로로, 크롱]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[뽀로로]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[루피, 에디]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[크롱, 뽀로로]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[루피]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -104,7 +738,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +751,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -143,8 +785,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -461,8 +1106,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7538E0A2-1BC0-4D45-B496-F703A763B3A4}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="11.375" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -489,22 +1141,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -512,24 +1164,236 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="G3">
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D13">
         <v>2</v>
       </c>
     </row>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57EDD4B5-ED9A-4093-AD1F-3843745B30CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5B5446-40D1-43AA-8111-E4731A176410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11325" xr2:uid="{C6E74B48-9CDE-4D63-A8F7-4935BA93D084}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
   <si>
     <t>질문</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -733,6 +733,34 @@
   </si>
   <si>
     <t>팀원으로서 중요한 덕목은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>답변C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>답변D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>답변E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sample3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sample4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sample5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sample2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1108,18 +1136,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7538E0A2-1BC0-4D45-B496-F703A763B3A4}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
     <col min="5" max="5" width="59.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1141,8 +1169,17 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1153,7 +1190,7 @@
         <v>48</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
@@ -1162,10 +1199,10 @@
         <v>38</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -1176,7 +1213,7 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -1185,10 +1222,10 @@
         <v>39</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1199,7 +1236,7 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -1208,10 +1245,10 @@
         <v>40</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1222,7 +1259,7 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -1231,10 +1268,10 @@
         <v>38</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1245,7 +1282,7 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -1254,10 +1291,10 @@
         <v>41</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1268,7 +1305,7 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
@@ -1277,10 +1314,10 @@
         <v>42</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1291,7 +1328,7 @@
         <v>42</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -1300,10 +1337,10 @@
         <v>43</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1314,7 +1351,7 @@
         <v>39</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
         <v>34</v>
@@ -1323,10 +1360,10 @@
         <v>44</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1337,7 +1374,7 @@
         <v>49</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -1346,10 +1383,10 @@
         <v>45</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1360,7 +1397,7 @@
         <v>45</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -1369,10 +1406,10 @@
         <v>46</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1383,7 +1420,7 @@
         <v>50</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
         <v>37</v>
@@ -1392,7 +1429,24 @@
         <v>47</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
